--- a/data/50001541 - XEMORTIZ MINERA FRISCO B.xlsx
+++ b/data/50001541 - XEMORTIZ MINERA FRISCO B.xlsx
@@ -2956,9 +2956,11 @@
       <c r="B15" s="8">
         <v>46132.58859509259</v>
       </c>
-      <c r="C15" s="9"/>
+      <c r="C15" s="8">
+        <v>46196.640665405095</v>
+      </c>
       <c r="D15" s="8">
-        <v>46183.87032850695</v>
+        <v>46196.64067877315</v>
       </c>
       <c r="E15" s="9" t="s">
         <v>60</v>
@@ -2993,9 +2995,11 @@
       <c r="Q15" s="9"/>
       <c r="R15" s="9"/>
       <c r="S15" s="9"/>
-      <c r="T15" s="9"/>
-      <c r="U15" s="12" t="s">
-        <v>58</v>
+      <c r="T15" s="9">
+        <v>1</v>
+      </c>
+      <c r="U15" s="11" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="16" spans="1:21" x14ac:dyDescent="0.25">
@@ -3330,9 +3334,11 @@
       <c r="B21" s="8">
         <v>46132.62798736111</v>
       </c>
-      <c r="C21" s="9"/>
+      <c r="C21" s="8">
+        <v>46196.64064614583</v>
+      </c>
       <c r="D21" s="8">
-        <v>46191.91766792824</v>
+        <v>46196.6430977662</v>
       </c>
       <c r="E21" s="9" t="s">
         <v>82</v>
@@ -3380,10 +3386,10 @@
         <v>32</v>
       </c>
       <c r="T21" s="9">
-        <v>0</v>
-      </c>
-      <c r="U21" s="12" t="s">
-        <v>58</v>
+        <v>1</v>
+      </c>
+      <c r="U21" s="11" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="22" spans="1:21" x14ac:dyDescent="0.25">
@@ -6275,7 +6281,7 @@
       </c>
       <c r="C72" s="6"/>
       <c r="D72" s="5">
-        <v>46178.16965391204</v>
+        <v>46196.640668113425</v>
       </c>
       <c r="E72" s="6" t="s">
         <v>83</v>
@@ -6325,8 +6331,8 @@
       <c r="T72" s="6">
         <v>0</v>
       </c>
-      <c r="U72" s="10" t="s">
-        <v>101</v>
+      <c r="U72" s="12" t="s">
+        <v>58</v>
       </c>
     </row>
     <row r="73" spans="1:21" x14ac:dyDescent="0.25">

--- a/data/50001541 - XEMORTIZ MINERA FRISCO B.xlsx
+++ b/data/50001541 - XEMORTIZ MINERA FRISCO B.xlsx
@@ -12086,7 +12086,7 @@
       </c>
       <c r="C179" s="9"/>
       <c r="D179" s="8">
-        <v>46134.579160567126</v>
+        <v>46216.19614337963</v>
       </c>
       <c r="E179" s="9" t="s">
         <v>397</v>
@@ -12128,8 +12128,8 @@
       <c r="R179" s="8">
         <v>46223</v>
       </c>
-      <c r="S179" s="11" t="s">
-        <v>97</v>
+      <c r="S179" s="12" t="s">
+        <v>308</v>
       </c>
       <c r="T179" s="9">
         <v>0</v>
